--- a/Simulador/base.xlsx
+++ b/Simulador/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Simulador/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="570" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{628D005C-0826-43F7-8573-0A282132A7D2}"/>
+  <xr:revisionPtr revIDLastSave="590" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DECA59-3221-499B-AD98-366AD9F0FFC4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
@@ -1502,10 +1502,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15141,7 +15137,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -15155,7 +15151,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>102</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
@@ -15169,7 +15165,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
         <v>462</v>
@@ -15183,7 +15179,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -16065,7 +16061,7 @@
         <v>12</v>
       </c>
       <c r="B70">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>25</v>
@@ -16079,7 +16075,7 @@
         <v>12</v>
       </c>
       <c r="B71">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>27</v>
@@ -16093,7 +16089,7 @@
         <v>12</v>
       </c>
       <c r="B72">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>462</v>
@@ -16107,7 +16103,7 @@
         <v>12</v>
       </c>
       <c r="B73">
-        <v>247</v>
+        <v>115</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>26</v>

--- a/Simulador/base.xlsx
+++ b/Simulador/base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Simulador/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="590" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DECA59-3221-499B-AD98-366AD9F0FFC4}"/>
+  <xr:revisionPtr revIDLastSave="609" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77FE3D7C-240D-4559-8250-A924CAE69731}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
@@ -1502,6 +1502,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15529,7 +15533,7 @@
         <v>5</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>23</v>
@@ -15557,7 +15561,7 @@
         <v>5</v>
       </c>
       <c r="B34">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>462</v>
@@ -15571,7 +15575,7 @@
         <v>5</v>
       </c>
       <c r="B35">
-        <v>92</v>
+        <v>219</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>27</v>
@@ -15585,7 +15589,7 @@
         <v>5</v>
       </c>
       <c r="B36">
-        <v>227</v>
+        <v>48</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>25</v>
@@ -15669,7 +15673,7 @@
         <v>6</v>
       </c>
       <c r="B42">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>26</v>
@@ -15963,7 +15967,7 @@
         <v>11</v>
       </c>
       <c r="B63">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>25</v>
@@ -15977,7 +15981,7 @@
         <v>11</v>
       </c>
       <c r="B64">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>24</v>
@@ -16005,7 +16009,7 @@
         <v>11</v>
       </c>
       <c r="B66">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>27</v>
@@ -16019,7 +16023,7 @@
         <v>11</v>
       </c>
       <c r="B67">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>462</v>
@@ -16145,7 +16149,7 @@
         <v>13</v>
       </c>
       <c r="B76">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>25</v>
@@ -16159,7 +16163,7 @@
         <v>13</v>
       </c>
       <c r="B77">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>24</v>
@@ -16173,7 +16177,7 @@
         <v>13</v>
       </c>
       <c r="B78">
-        <v>73</v>
+        <v>296</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>462</v>
@@ -16215,7 +16219,7 @@
         <v>14</v>
       </c>
       <c r="B81">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>24</v>
@@ -16243,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="B83">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>462</v>
@@ -16257,7 +16261,7 @@
         <v>14</v>
       </c>
       <c r="B84">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>27</v>
@@ -16271,7 +16275,7 @@
         <v>14</v>
       </c>
       <c r="B85">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>26</v>
